--- a/assets/constructions/examples/ctd_inserts_gears.xlsx
+++ b/assets/constructions/examples/ctd_inserts_gears.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,11 +589,36 @@
           <t>adintws</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5UTEW340M6.0Z55-5480GMVTX</t>
+          <t>2UEW25M1.0Z24-5480GMVTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -614,7 +639,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5UT</t>
+          <t>2U</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -640,42 +665,42 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5UTEW340M6.0Z55-5480GM</t>
+          <t>2UEW25M1.0Z24-5480GM</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="V2" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>340</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -703,19 +728,38 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>VARGUS_5/8UT_GM</t>
+          <t>VARGUS_1/4U_GM</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>4061.05</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3UEW32M2.0Z14-5480GMVTX</t>
+          <t>3UEW80M2.0Z38-5480GMVTX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -760,7 +804,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3UEW32M2.0Z14-5480GM</t>
+          <t>3UEW80M2.0Z38-5480GM</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -781,13 +825,13 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="U3" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -795,7 +839,7 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -829,13 +873,32 @@
       <c r="AF3" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>4482.89</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5UEW85M3.0Z27-5480GMVTX</t>
+          <t>4UEM2.0Z17-20N3GMVBX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -856,7 +919,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5U</t>
+          <t>4U</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -866,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -882,7 +945,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5UEW85M3.0Z27-5480GM</t>
+          <t>4UEM2.0Z17-20N3GM</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -892,36 +955,34 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="U4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>85</v>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>DIN 5480</t>
+          <t>DIN 3972 Basic Profile I</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -940,24 +1001,43 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>VARGUS_5/8U_GM</t>
+          <t>VARGUS_1/2U_GM</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>10356.96</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5UEW80M3.0Z25-5480GMVTX</t>
+          <t>4UEW80M2.5Z30-5480GMVTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -978,7 +1058,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5U</t>
+          <t>4U</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -996,15 +1076,13 @@
           <t>N</t>
         </is>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5UEW80M3.0Z25-5480GM</t>
+          <t>4UEW80M2.5Z30-5480GM</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1014,28 +1092,28 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="U5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1049,7 +1127,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022/VARGUS Обработка шлицев и зубчатых колёс</t>
+          <t>2021 / NPA 56 Gear_Milling_Expanded Line 140621.pdf</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1062,24 +1140,43 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>CVD</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>VARGUS_5/8U_GM</t>
+          <t>VARGUS_1/2U_GM</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>135.04</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>11867.67</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2UEDP32/64Z12-13N2GMVBX</t>
+          <t>2UEDP32/64Z55-135N8GMVBX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1124,7 +1221,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2UEDP32/64Z12-13N2GM</t>
+          <t>2UEDP32/64Z55-135N8GM</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -1143,13 +1240,13 @@
         <v>64</v>
       </c>
       <c r="T6" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="U6" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1189,6 +1286,25 @@
       <c r="AF6" t="inlineStr">
         <is>
           <t>WORKPIECE</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>102.41</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>9000.059999999999</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
